--- a/REST.xlsx
+++ b/REST.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jakob\g1t2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC19F153-0902-40B5-B929-27246774A6A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8040" windowHeight="9705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Frontend &lt;-&gt; Backend" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="DTO" sheetId="2" r:id="rId5"/>
+    <sheet name="Frontend &lt;-&gt; Backend" sheetId="1" r:id="rId1"/>
+    <sheet name="DTO" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -288,9 +297,6 @@
     <t>Create a new order from the users current shoppingCart</t>
   </si>
   <si>
-    <t>OrderCreateDTO</t>
-  </si>
-  <si>
     <t>Delete an order</t>
   </si>
   <si>
@@ -544,99 +550,109 @@
   </si>
   <si>
     <t>UserxRole[]</t>
+  </si>
+  <si>
+    <t>CartDTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="17">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Menlo"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;\0022Helvetica Neue\0022&quot;"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Menlo"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -647,7 +663,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -711,7 +727,13 @@
     </fill>
   </fills>
   <borders count="6">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -725,19 +747,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -747,6 +773,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -758,204 +785,178 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="11" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8E7FC"/>
+          <bgColor rgb="FFE8E7FC"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8989EB"/>
           <bgColor rgb="FF8989EB"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE8E7FC"/>
-          <bgColor rgb="FFE8E7FC"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Frontend &lt;-&gt; Backend-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Frontend &lt;-&gt; Backend-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I28" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:I28">
   <tableColumns count="9">
-    <tableColumn name="URI-Template" id="1"/>
-    <tableColumn name="Controller" id="2"/>
-    <tableColumn name="Description" id="3"/>
-    <tableColumn name="HTTP Method" id="4"/>
-    <tableColumn name="Path Parameter(s) + Type(s)" id="5"/>
-    <tableColumn name="Request Body + Type" id="6"/>
-    <tableColumn name="Response Code" id="7"/>
-    <tableColumn name="Response + Type" id="8"/>
-    <tableColumn name="Comments" id="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="URI-Template"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Controller"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="HTTP Method"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Path Parameter(s) + Type(s)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Request Body + Type"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Response Code"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Response + Type"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Comments"/>
   </tableColumns>
-  <tableStyleInfo name="Frontend &lt;-&gt; Backend-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Frontend &lt;-&gt; Backend-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1145,28 +1146,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.0"/>
-    <col customWidth="1" min="2" max="2" width="21.75"/>
-    <col customWidth="1" min="3" max="3" width="49.88"/>
-    <col customWidth="1" min="4" max="4" width="17.0"/>
-    <col customWidth="1" min="5" max="5" width="28.88"/>
-    <col customWidth="1" min="6" max="6" width="23.63"/>
-    <col customWidth="1" min="7" max="8" width="20.13"/>
-    <col customWidth="1" min="9" max="9" width="24.63"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="8" width="20.140625" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="31.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1218,7 +1222,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" ht="12.75">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1241,7 +1245,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" ht="12.75">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1266,7 +1270,7 @@
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" ht="12.75">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" ht="12.75">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -1316,7 +1320,7 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" ht="12.75">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
@@ -1341,7 +1345,7 @@
       </c>
       <c r="I7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" ht="12.75">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -1364,7 +1368,7 @@
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" ht="12.75">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1387,7 +1391,7 @@
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" ht="25.5">
       <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
@@ -1412,7 +1416,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>44</v>
       </c>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:9" ht="12.75">
       <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
@@ -1464,7 +1468,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:9" ht="12.75">
       <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
@@ -1493,7 +1497,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:9" ht="12.75">
       <c r="A14" s="5" t="s">
         <v>50</v>
       </c>
@@ -1518,7 +1522,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" spans="1:9" ht="17.25" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>53</v>
       </c>
@@ -1543,7 +1547,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:9" ht="25.5">
       <c r="A16" s="7" t="s">
         <v>58</v>
       </c>
@@ -1570,7 +1574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:9" ht="25.5">
       <c r="A17" s="7" t="s">
         <v>62</v>
       </c>
@@ -1595,7 +1599,7 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:9" ht="12.75">
       <c r="A18" s="7" t="s">
         <v>58</v>
       </c>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:9" ht="25.5">
       <c r="A19" s="7" t="s">
         <v>53</v>
       </c>
@@ -1649,7 +1653,7 @@
       </c>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
+    <row r="20" spans="1:9" ht="16.5" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>68</v>
       </c>
@@ -1674,7 +1678,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:9" ht="12.75">
       <c r="A21" s="9" t="s">
         <v>68</v>
       </c>
@@ -1695,7 +1699,7 @@
       <c r="H21" s="10"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:9" ht="25.5">
       <c r="A22" s="9" t="s">
         <v>74</v>
       </c>
@@ -1722,7 +1726,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:9" ht="12.75">
       <c r="A23" s="9" t="s">
         <v>74</v>
       </c>
@@ -1749,7 +1753,7 @@
       </c>
       <c r="I23" s="9"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:9" ht="12.75">
       <c r="A24" s="9" t="s">
         <v>74</v>
       </c>
@@ -1772,7 +1776,7 @@
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
+    <row r="25" spans="1:9" ht="16.5" customHeight="1">
       <c r="A25" s="11" t="s">
         <v>83</v>
       </c>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="I25" s="12"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:9" ht="12.75">
       <c r="A26" s="11" t="s">
         <v>87</v>
       </c>
@@ -1820,7 +1824,7 @@
       </c>
       <c r="I26" s="12"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:9" ht="12.75">
       <c r="A27" s="11" t="s">
         <v>83</v>
       </c>
@@ -1835,7 +1839,7 @@
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="11" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>25</v>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="I27" s="12"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:9" ht="12.75">
       <c r="A28" s="13" t="s">
         <v>87</v>
       </c>
@@ -1853,7 +1857,7 @@
         <v>84</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>12</v>
@@ -1870,1341 +1874,1358 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
-  <pageSetup paperSize="9" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" pageOrder="overThenDown" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:BN31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.63"/>
-    <col customWidth="1" min="5" max="5" width="13.38"/>
-    <col customWidth="1" min="7" max="7" width="15.25"/>
-    <col customWidth="1" min="8" max="8" width="15.0"/>
-    <col customWidth="1" min="10" max="10" width="16.25"/>
-    <col customWidth="1" min="11" max="11" width="14.13"/>
-    <col customWidth="1" min="14" max="14" width="15.38"/>
-    <col customWidth="1" min="17" max="17" width="12.5"/>
-    <col customWidth="1" min="20" max="20" width="20.13"/>
-    <col customWidth="1" min="21" max="21" width="9.75"/>
-    <col customWidth="1" min="22" max="22" width="20.88"/>
-    <col customWidth="1" min="23" max="23" width="20.38"/>
-    <col customWidth="1" min="24" max="24" width="12.13"/>
-    <col customWidth="1" min="25" max="25" width="14.63"/>
-    <col customWidth="1" min="26" max="27" width="14.13"/>
-    <col customWidth="1" min="28" max="28" width="20.63"/>
-    <col customWidth="1" min="29" max="31" width="14.13"/>
-    <col customWidth="1" min="32" max="32" width="22.0"/>
-    <col customWidth="1" min="33" max="66" width="14.13"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" customWidth="1"/>
+    <col min="20" max="20" width="20.140625" customWidth="1"/>
+    <col min="21" max="21" width="9.7109375" customWidth="1"/>
+    <col min="22" max="22" width="20.85546875" customWidth="1"/>
+    <col min="23" max="23" width="20.42578125" customWidth="1"/>
+    <col min="24" max="24" width="12.140625" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" customWidth="1"/>
+    <col min="26" max="27" width="14.140625" customWidth="1"/>
+    <col min="28" max="28" width="20.5703125" customWidth="1"/>
+    <col min="29" max="31" width="14.140625" customWidth="1"/>
+    <col min="32" max="32" width="22" customWidth="1"/>
+    <col min="33" max="66" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:66" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="D1" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="32"/>
+      <c r="G1" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="32"/>
+      <c r="J1" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="J1" s="15" t="s">
+      <c r="K1" s="32"/>
+      <c r="M1" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="32"/>
+      <c r="P1" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="16"/>
-      <c r="P1" s="15" t="s">
+      <c r="Q1" s="32"/>
+      <c r="V1" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="32"/>
+      <c r="Y1" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="Y1" s="15" t="s">
+      <c r="Z1" s="32"/>
+      <c r="AB1" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="Z1" s="16"/>
-      <c r="AB1" s="15" t="s">
+      <c r="AC1" s="32"/>
+      <c r="AE1" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AE1" s="17" t="s">
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="17" t="s">
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="16"/>
+      <c r="AS1" s="16"/>
+      <c r="AT1" s="16"/>
+      <c r="AU1" s="16"/>
+      <c r="AV1" s="16"/>
+      <c r="AW1" s="16"/>
+      <c r="AX1" s="16"/>
+      <c r="AY1" s="16"/>
+      <c r="AZ1" s="16"/>
+      <c r="BA1" s="16"/>
+      <c r="BB1" s="16"/>
+      <c r="BC1" s="16"/>
+      <c r="BD1" s="16"/>
+      <c r="BE1" s="16"/>
+      <c r="BF1" s="16"/>
+      <c r="BG1" s="16"/>
+      <c r="BH1" s="16"/>
+      <c r="BI1" s="16"/>
+      <c r="BJ1" s="16"/>
+      <c r="BK1" s="16"/>
+      <c r="BL1" s="16"/>
+      <c r="BM1" s="16"/>
+      <c r="BN1" s="16"/>
+    </row>
+    <row r="2" spans="1:66" ht="15.75" customHeight="1">
+      <c r="A2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="19"/>
-      <c r="AK1" s="19"/>
-      <c r="AL1" s="19"/>
-      <c r="AM1" s="19"/>
-      <c r="AN1" s="19"/>
-      <c r="AO1" s="19"/>
-      <c r="AP1" s="19"/>
-      <c r="AQ1" s="19"/>
-      <c r="AR1" s="19"/>
-      <c r="AS1" s="19"/>
-      <c r="AT1" s="19"/>
-      <c r="AU1" s="19"/>
-      <c r="AV1" s="19"/>
-      <c r="AW1" s="19"/>
-      <c r="AX1" s="19"/>
-      <c r="AY1" s="19"/>
-      <c r="AZ1" s="19"/>
-      <c r="BA1" s="19"/>
-      <c r="BB1" s="19"/>
-      <c r="BC1" s="19"/>
-      <c r="BD1" s="19"/>
-      <c r="BE1" s="19"/>
-      <c r="BF1" s="19"/>
-      <c r="BG1" s="19"/>
-      <c r="BH1" s="19"/>
-      <c r="BI1" s="19"/>
-      <c r="BJ1" s="19"/>
-      <c r="BK1" s="19"/>
-      <c r="BL1" s="19"/>
-      <c r="BM1" s="19"/>
-      <c r="BN1" s="19"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="D2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="T2" s="32"/>
+      <c r="V2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="W2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="20" t="s">
+      <c r="Y2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="20" t="s">
+      <c r="AB2" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="K2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="M2" s="20" t="s">
+      <c r="AE2" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF2" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="N2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" s="20" t="s">
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI2" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="Q2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="S2" s="15" t="s">
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
+      <c r="AO2" s="16"/>
+      <c r="AP2" s="16"/>
+      <c r="AQ2" s="16"/>
+      <c r="AR2" s="16"/>
+      <c r="AS2" s="16"/>
+      <c r="AT2" s="16"/>
+      <c r="AU2" s="16"/>
+      <c r="AV2" s="16"/>
+      <c r="AW2" s="16"/>
+      <c r="AX2" s="16"/>
+      <c r="AY2" s="16"/>
+      <c r="AZ2" s="16"/>
+      <c r="BA2" s="16"/>
+      <c r="BB2" s="16"/>
+      <c r="BC2" s="16"/>
+      <c r="BD2" s="16"/>
+      <c r="BE2" s="16"/>
+      <c r="BF2" s="16"/>
+      <c r="BG2" s="16"/>
+      <c r="BH2" s="16"/>
+      <c r="BI2" s="16"/>
+      <c r="BJ2" s="16"/>
+      <c r="BK2" s="16"/>
+      <c r="BL2" s="16"/>
+      <c r="BM2" s="16"/>
+      <c r="BN2" s="16"/>
+    </row>
+    <row r="3" spans="1:66">
+      <c r="A3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="T2" s="16"/>
-      <c r="V2" s="20" t="s">
+      <c r="B3" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="T3" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="W2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y2" s="20" t="s">
+      <c r="V3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="W3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB3" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="AC3" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE3" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF3" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG3" s="15"/>
+      <c r="AH3" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI3" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="23"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="23"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23"/>
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="23"/>
+      <c r="BJ3" s="23"/>
+      <c r="BK3" s="23"/>
+      <c r="BL3" s="23"/>
+      <c r="BM3" s="23"/>
+      <c r="BN3" s="23"/>
+    </row>
+    <row r="4" spans="1:66">
+      <c r="A4" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="T4" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="W4" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y4" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z4" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB4" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC4" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ4" s="23"/>
+      <c r="AK4" s="23"/>
+      <c r="AL4" s="23"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="23"/>
+      <c r="AW4" s="23"/>
+      <c r="AX4" s="23"/>
+      <c r="AY4" s="23"/>
+      <c r="AZ4" s="23"/>
+      <c r="BA4" s="23"/>
+      <c r="BB4" s="23"/>
+      <c r="BC4" s="23"/>
+      <c r="BD4" s="23"/>
+      <c r="BE4" s="23"/>
+      <c r="BF4" s="23"/>
+      <c r="BG4" s="23"/>
+      <c r="BH4" s="23"/>
+      <c r="BI4" s="23"/>
+      <c r="BJ4" s="23"/>
+      <c r="BK4" s="23"/>
+      <c r="BL4" s="23"/>
+      <c r="BM4" s="23"/>
+      <c r="BN4" s="23"/>
+    </row>
+    <row r="5" spans="1:66">
+      <c r="A5" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="T5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="W5" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y5" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AE5" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF5" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ5" s="23"/>
+      <c r="AK5" s="23"/>
+      <c r="AL5" s="23"/>
+      <c r="AM5" s="23"/>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="23"/>
+      <c r="AQ5" s="23"/>
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="23"/>
+      <c r="AT5" s="23"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23"/>
+      <c r="AX5" s="23"/>
+      <c r="AY5" s="23"/>
+      <c r="AZ5" s="23"/>
+      <c r="BA5" s="23"/>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="23"/>
+      <c r="BD5" s="23"/>
+      <c r="BE5" s="23"/>
+      <c r="BF5" s="23"/>
+      <c r="BG5" s="23"/>
+      <c r="BH5" s="23"/>
+      <c r="BI5" s="23"/>
+      <c r="BJ5" s="23"/>
+      <c r="BK5" s="23"/>
+      <c r="BL5" s="23"/>
+      <c r="BM5" s="23"/>
+      <c r="BN5" s="23"/>
+    </row>
+    <row r="6" spans="1:66" ht="15.75" customHeight="1">
+      <c r="A6" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="32"/>
+      <c r="J6" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q6" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="T6" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="Y6" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AE6" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF6" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI6" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="AJ6" s="23"/>
+      <c r="AK6" s="23"/>
+      <c r="AL6" s="23"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="23"/>
+      <c r="BA6" s="23"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="23"/>
+      <c r="BD6" s="23"/>
+      <c r="BE6" s="23"/>
+      <c r="BF6" s="23"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="23"/>
+      <c r="BI6" s="23"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
+      <c r="BM6" s="23"/>
+      <c r="BN6" s="23"/>
+    </row>
+    <row r="7" spans="1:66">
+      <c r="A7" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="Z2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB2" s="20" t="s">
+      <c r="J7" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="P7" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="T7" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE7" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF7" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="AI7" s="24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:66">
+      <c r="A8" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="S8" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="T8" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE8" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF8" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG8" s="15"/>
+      <c r="AH8" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI8" s="24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:66">
+      <c r="A9" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="T9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
+      <c r="AH9" s="15"/>
+      <c r="AI9" s="15"/>
+    </row>
+    <row r="10" spans="1:66">
+      <c r="A10" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+    </row>
+    <row r="11" spans="1:66">
+      <c r="A11" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE11" s="15"/>
+      <c r="AF11" s="15"/>
+      <c r="AG11" s="15"/>
+      <c r="AH11" s="15"/>
+      <c r="AI11" s="15"/>
+    </row>
+    <row r="12" spans="1:66">
+      <c r="A12" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+    </row>
+    <row r="13" spans="1:66">
+      <c r="A13" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE13" s="15"/>
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="15"/>
+      <c r="AH13" s="15"/>
+      <c r="AI13" s="15"/>
+    </row>
+    <row r="14" spans="1:66">
+      <c r="A14" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE14" s="15"/>
+      <c r="AF14" s="15"/>
+      <c r="AG14" s="15"/>
+      <c r="AH14" s="15"/>
+      <c r="AI14" s="15"/>
+    </row>
+    <row r="15" spans="1:66">
+      <c r="AE15" s="15"/>
+      <c r="AF15" s="15"/>
+      <c r="AG15" s="15"/>
+      <c r="AH15" s="15"/>
+      <c r="AI15" s="15"/>
+    </row>
+    <row r="16" spans="1:66">
+      <c r="AE16" s="15"/>
+      <c r="AF16" s="15"/>
+      <c r="AG16" s="15"/>
+      <c r="AH16" s="15"/>
+      <c r="AI16" s="15"/>
+    </row>
+    <row r="17" spans="1:35" ht="15.75" customHeight="1">
+      <c r="A17" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="37"/>
+      <c r="G17" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="32"/>
+      <c r="J17" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="K17" s="32"/>
+      <c r="P17" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q17" s="32"/>
+      <c r="V17" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="W17" s="32"/>
+      <c r="Y17" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z17" s="32"/>
+      <c r="AE17" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="AF17" s="32"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI17" s="32"/>
+    </row>
+    <row r="18" spans="1:35" ht="15.75" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AC2" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="AE2" s="21" t="s">
+      <c r="D18" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="AF2" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="21" t="s">
+      <c r="G18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="AI2" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
-      <c r="AP2" s="19"/>
-      <c r="AQ2" s="19"/>
-      <c r="AR2" s="19"/>
-      <c r="AS2" s="19"/>
-      <c r="AT2" s="19"/>
-      <c r="AU2" s="19"/>
-      <c r="AV2" s="19"/>
-      <c r="AW2" s="19"/>
-      <c r="AX2" s="19"/>
-      <c r="AY2" s="19"/>
-      <c r="AZ2" s="19"/>
-      <c r="BA2" s="19"/>
-      <c r="BB2" s="19"/>
-      <c r="BC2" s="19"/>
-      <c r="BD2" s="19"/>
-      <c r="BE2" s="19"/>
-      <c r="BF2" s="19"/>
-      <c r="BG2" s="19"/>
-      <c r="BH2" s="19"/>
-      <c r="BI2" s="19"/>
-      <c r="BJ2" s="19"/>
-      <c r="BK2" s="19"/>
-      <c r="BL2" s="19"/>
-      <c r="BM2" s="19"/>
-      <c r="BN2" s="19"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="J18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="S18" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="T18" s="32"/>
+      <c r="V18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="W18" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z18" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE18" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF18" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG18" s="15"/>
+      <c r="AH18" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI18" s="18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35">
+      <c r="A19" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E19" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="P19" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="S19" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="V19" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="W19" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y19" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z19" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE19" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF19" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG19" s="15"/>
+      <c r="AH19" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI19" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35">
+      <c r="A20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="P20" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q20" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="T20" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="W20" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y20" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z20" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE20" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF20" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG20" s="15"/>
+      <c r="AH20" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI20" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35">
+      <c r="A21" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="J21" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="P21" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q21" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="T21" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="V21" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="W21" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y21" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z21" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE21" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF21" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG21" s="15"/>
+      <c r="AH21" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI21" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35">
+      <c r="A22" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="J22" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="P22" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="S22" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="T22" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="Y22" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z22" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE22" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF22" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG22" s="15"/>
+      <c r="AH22" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI22" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" ht="15.75" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="G23" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23" s="32"/>
+      <c r="J23" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="P23" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="S23" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="T23" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE23" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF23" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG23" s="15"/>
+      <c r="AH23" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="AI23" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35">
+      <c r="A24" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="P24" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q24" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="S24" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="T24" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE24" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF24" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI24" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35">
+      <c r="A25" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E25" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="P25" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q25" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="22" t="s">
+      <c r="S25" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="T25" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="M3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="P3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="T3" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="V3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB3" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC3" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE3" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AF3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG3" s="18"/>
-      <c r="AH3" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI3" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="26"/>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="26"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="26"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="26"/>
-      <c r="BL3" s="26"/>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="K4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="P4" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="T4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="W4" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB4" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC4" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="AE4" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF4" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI4" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ4" s="26"/>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="26"/>
-      <c r="AM4" s="26"/>
-      <c r="AN4" s="26"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="26"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="26"/>
-      <c r="AS4" s="26"/>
-      <c r="AT4" s="26"/>
-      <c r="AU4" s="26"/>
-      <c r="AV4" s="26"/>
-      <c r="AW4" s="26"/>
-      <c r="AX4" s="26"/>
-      <c r="AY4" s="26"/>
-      <c r="AZ4" s="26"/>
-      <c r="BA4" s="26"/>
-      <c r="BB4" s="26"/>
-      <c r="BC4" s="26"/>
-      <c r="BD4" s="26"/>
-      <c r="BE4" s="26"/>
-      <c r="BF4" s="26"/>
-      <c r="BG4" s="26"/>
-      <c r="BH4" s="26"/>
-      <c r="BI4" s="26"/>
-      <c r="BJ4" s="26"/>
-      <c r="BK4" s="26"/>
-      <c r="BL4" s="26"/>
-      <c r="BM4" s="26"/>
-      <c r="BN4" s="26"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="22" t="s">
+    </row>
+    <row r="26" spans="1:35">
+      <c r="A26" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="P5" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S5" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="T5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V5" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="W5" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y5" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z5" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AE5" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF5" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="AG5" s="18"/>
-      <c r="AH5" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI5" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ5" s="26"/>
-      <c r="AK5" s="26"/>
-      <c r="AL5" s="26"/>
-      <c r="AM5" s="26"/>
-      <c r="AN5" s="26"/>
-      <c r="AO5" s="26"/>
-      <c r="AP5" s="26"/>
-      <c r="AQ5" s="26"/>
-      <c r="AR5" s="26"/>
-      <c r="AS5" s="26"/>
-      <c r="AT5" s="26"/>
-      <c r="AU5" s="26"/>
-      <c r="AV5" s="26"/>
-      <c r="AW5" s="26"/>
-      <c r="AX5" s="26"/>
-      <c r="AY5" s="26"/>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="26"/>
-      <c r="BC5" s="26"/>
-      <c r="BD5" s="26"/>
-      <c r="BE5" s="26"/>
-      <c r="BF5" s="26"/>
-      <c r="BG5" s="26"/>
-      <c r="BH5" s="26"/>
-      <c r="BI5" s="26"/>
-      <c r="BJ5" s="26"/>
-      <c r="BK5" s="26"/>
-      <c r="BL5" s="26"/>
-      <c r="BM5" s="26"/>
-      <c r="BN5" s="26"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="22" t="s">
+      <c r="B26" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35">
+      <c r="A27" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="J6" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="N6" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q6" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="S6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="T6" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="Y6" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z6" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AE6" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF6" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI6" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="AJ6" s="26"/>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="26"/>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
-      <c r="AS6" s="26"/>
-      <c r="AT6" s="26"/>
-      <c r="AU6" s="26"/>
-      <c r="AV6" s="26"/>
-      <c r="AW6" s="26"/>
-      <c r="AX6" s="26"/>
-      <c r="AY6" s="26"/>
-      <c r="AZ6" s="26"/>
-      <c r="BA6" s="26"/>
-      <c r="BB6" s="26"/>
-      <c r="BC6" s="26"/>
-      <c r="BD6" s="26"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
-      <c r="BG6" s="26"/>
-      <c r="BH6" s="26"/>
-      <c r="BI6" s="26"/>
-      <c r="BJ6" s="26"/>
-      <c r="BK6" s="26"/>
-      <c r="BL6" s="26"/>
-      <c r="BM6" s="26"/>
-      <c r="BN6" s="26"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="s">
+      <c r="B27" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35">
+      <c r="A28" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="P7" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q7" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="S7" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="T7" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE7" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF7" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="27" t="s">
+      <c r="B28" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35">
+      <c r="A29" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="AI7" s="27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="P8" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q8" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="S8" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="T8" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE8" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="AF8" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="AG8" s="18"/>
-      <c r="AH8" s="27" t="s">
+      <c r="B29" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35">
+      <c r="A30" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="AI8" s="27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="22" t="s">
+      <c r="B30" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="P9" s="24" t="s">
+    </row>
+    <row r="31" spans="1:35">
+      <c r="A31" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="Q9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S9" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="T9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="18"/>
-      <c r="AG9" s="18"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="18"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE10" s="18"/>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="18"/>
-      <c r="AH10" s="18"/>
-      <c r="AI10" s="18"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE11" s="18"/>
-      <c r="AF11" s="18"/>
-      <c r="AG11" s="18"/>
-      <c r="AH11" s="18"/>
-      <c r="AI11" s="18"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE12" s="18"/>
-      <c r="AF12" s="18"/>
-      <c r="AG12" s="18"/>
-      <c r="AH12" s="18"/>
-      <c r="AI12" s="18"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="AE13" s="18"/>
-      <c r="AF13" s="18"/>
-      <c r="AG13" s="18"/>
-      <c r="AH13" s="18"/>
-      <c r="AI13" s="18"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="AE14" s="18"/>
-      <c r="AF14" s="18"/>
-      <c r="AG14" s="18"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="18"/>
-    </row>
-    <row r="15">
-      <c r="AE15" s="18"/>
-      <c r="AF15" s="18"/>
-      <c r="AG15" s="18"/>
-      <c r="AH15" s="18"/>
-      <c r="AI15" s="18"/>
-    </row>
-    <row r="16">
-      <c r="AE16" s="18"/>
-      <c r="AF16" s="18"/>
-      <c r="AG16" s="18"/>
-      <c r="AH16" s="18"/>
-      <c r="AI16" s="18"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="D17" s="31"/>
-      <c r="G17" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="J17" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="P17" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q17" s="16"/>
-      <c r="V17" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="W17" s="16"/>
-      <c r="Y17" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z17" s="16"/>
-      <c r="AE17" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="18"/>
-      <c r="AH17" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI17" s="16"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="S18" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="T18" s="16"/>
-      <c r="V18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="W18" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z18" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="AE18" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AF18" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="AG18" s="18"/>
-      <c r="AH18" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI18" s="21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="P19" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q19" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="S19" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="T19" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="V19" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="W19" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y19" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z19" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE19" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AF19" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG19" s="18"/>
-      <c r="AH19" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI19" s="25" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="P20" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q20" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S20" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="T20" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V20" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="W20" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y20" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z20" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE20" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="AF20" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG20" s="18"/>
-      <c r="AH20" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI20" s="25" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="J21" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="K21" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="P21" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q21" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S21" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="T21" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V21" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="W21" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y21" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="Z21" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE21" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF21" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG21" s="18"/>
-      <c r="AH21" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI21" s="27" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="J22" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="P22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q22" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="S22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="T22" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="Y22" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z22" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE22" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="AF22" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="AG22" s="18"/>
-      <c r="AH22" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI22" s="25" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="D23" s="31"/>
-      <c r="G23" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="H23" s="16"/>
-      <c r="J23" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="K23" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="P23" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q23" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="S23" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="T23" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE23" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF23" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="AG23" s="18"/>
-      <c r="AH23" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="AI23" s="27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="P24" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q24" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="S24" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="T24" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE24" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="AF24" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="AG24" s="18"/>
-      <c r="AH24" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="AI24" s="27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="s">
+      <c r="B31" s="19" t="s">
         <v>175</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="P25" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q25" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="S25" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="T25" s="24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="AH17:AI17"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AE1:AF1"/>
@@ -3215,22 +3236,7 @@
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="AE17:AF17"/>
-    <mergeCell ref="AH17:AI17"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="P17:Q17"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/REST.xlsx
+++ b/REST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jakob\g1t2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC19F153-0902-40B5-B929-27246774A6A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E637B31-3B1A-456F-8EE4-D8EF48431792}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8040" windowHeight="9705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Frontend &lt;-&gt; Backend" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="181">
   <si>
     <t>URI-Template</t>
   </si>
@@ -405,9 +405,6 @@
     <t>Collection&lt;CartItemDTO&gt;</t>
   </si>
   <si>
-    <t>Collection&lt;OrderItemDTO&gt;</t>
-  </si>
-  <si>
     <t>productName</t>
   </si>
   <si>
@@ -450,21 +447,12 @@
     <t>OrderStatus</t>
   </si>
   <si>
-    <t>priceAtOrder</t>
-  </si>
-  <si>
     <t>phone</t>
   </si>
   <si>
     <t>discount</t>
   </si>
   <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>discountAtOrder</t>
-  </si>
-  <si>
     <t>enabled</t>
   </si>
   <si>
@@ -552,7 +540,31 @@
     <t>UserxRole[]</t>
   </si>
   <si>
-    <t>CartDTO</t>
+    <t>CheckoutRequestDTO</t>
+  </si>
+  <si>
+    <t>orderDate</t>
+  </si>
+  <si>
+    <t>List&lt;OrderItemDTO&gt;</t>
+  </si>
+  <si>
+    <t>shippingName</t>
+  </si>
+  <si>
+    <t>paymentMethod</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>priceAtOPurchase</t>
+  </si>
+  <si>
+    <t>discountAtPurchase</t>
   </si>
 </sst>
 </file>
@@ -873,23 +885,23 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1839,10 +1851,10 @@
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>89</v>
@@ -1908,52 +1920,54 @@
     <col min="28" max="28" width="20.5703125" customWidth="1"/>
     <col min="29" max="31" width="14.140625" customWidth="1"/>
     <col min="32" max="32" width="22" customWidth="1"/>
-    <col min="33" max="66" width="14.140625" customWidth="1"/>
+    <col min="33" max="33" width="14.140625" customWidth="1"/>
+    <col min="34" max="34" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="66" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>92</v>
       </c>
       <c r="B1" s="32"/>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="35" t="s">
         <v>93</v>
       </c>
       <c r="E1" s="32"/>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="35" t="s">
         <v>94</v>
       </c>
       <c r="H1" s="32"/>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="35" t="s">
         <v>95</v>
       </c>
       <c r="K1" s="32"/>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="35" t="s">
         <v>96</v>
       </c>
       <c r="N1" s="32"/>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="35" t="s">
         <v>97</v>
       </c>
       <c r="Q1" s="32"/>
-      <c r="V1" s="31" t="s">
+      <c r="V1" s="35" t="s">
         <v>98</v>
       </c>
       <c r="W1" s="32"/>
-      <c r="Y1" s="31" t="s">
+      <c r="Y1" s="35" t="s">
         <v>99</v>
       </c>
       <c r="Z1" s="32"/>
-      <c r="AB1" s="31" t="s">
+      <c r="AB1" s="35" t="s">
         <v>100</v>
       </c>
       <c r="AC1" s="32"/>
-      <c r="AE1" s="33" t="s">
+      <c r="AE1" s="37" t="s">
         <v>101</v>
       </c>
       <c r="AF1" s="32"/>
       <c r="AG1" s="15"/>
-      <c r="AH1" s="33" t="s">
+      <c r="AH1" s="37" t="s">
         <v>102</v>
       </c>
       <c r="AI1" s="32"/>
@@ -2026,7 +2040,7 @@
       <c r="Q2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="S2" s="35" t="s">
         <v>105</v>
       </c>
       <c r="T2" s="32"/>
@@ -2093,7 +2107,7 @@
       <c r="BM2" s="16"/>
       <c r="BN2" s="16"/>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:66" ht="15">
       <c r="A3" s="19" t="s">
         <v>106</v>
       </c>
@@ -2161,10 +2175,10 @@
         <v>107</v>
       </c>
       <c r="AG3" s="15"/>
-      <c r="AH3" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI3" s="22" t="s">
+      <c r="AH3" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI3" s="24" t="s">
         <v>107</v>
       </c>
       <c r="AJ3" s="23"/>
@@ -2199,7 +2213,7 @@
       <c r="BM3" s="23"/>
       <c r="BN3" s="23"/>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:66" ht="12.75">
       <c r="A4" s="19" t="s">
         <v>111</v>
       </c>
@@ -2255,17 +2269,17 @@
         <v>118</v>
       </c>
       <c r="AE4" s="24" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="AF4" s="24" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="AG4" s="15"/>
       <c r="AH4" s="24" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="AI4" s="24" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="AJ4" s="23"/>
       <c r="AK4" s="23"/>
@@ -2299,7 +2313,7 @@
       <c r="BM4" s="23"/>
       <c r="BN4" s="23"/>
     </row>
-    <row r="5" spans="1:66">
+    <row r="5" spans="1:66" ht="12.75">
       <c r="A5" s="19" t="s">
         <v>119</v>
       </c>
@@ -2351,17 +2365,17 @@
       <c r="AB5" s="23"/>
       <c r="AC5" s="23"/>
       <c r="AE5" s="24" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AF5" s="24" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="AG5" s="15"/>
       <c r="AH5" s="24" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="AI5" s="24" t="s">
-        <v>36</v>
+        <v>178</v>
       </c>
       <c r="AJ5" s="23"/>
       <c r="AK5" s="23"/>
@@ -2397,44 +2411,44 @@
     </row>
     <row r="6" spans="1:66" ht="15.75" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>107</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="31" t="s">
-        <v>131</v>
+      <c r="G6" s="35" t="s">
+        <v>130</v>
       </c>
       <c r="H6" s="32"/>
       <c r="J6" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K6" s="21" t="s">
         <v>36</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N6" s="25" t="s">
         <v>36</v>
       </c>
       <c r="P6" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q6" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="Q6" s="21" t="s">
-        <v>134</v>
-      </c>
       <c r="S6" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="T6" s="21" t="s">
         <v>133</v>
-      </c>
-      <c r="T6" s="21" t="s">
-        <v>134</v>
       </c>
       <c r="V6" s="23"/>
       <c r="W6" s="23"/>
@@ -2447,17 +2461,17 @@
       <c r="AB6" s="23"/>
       <c r="AC6" s="23"/>
       <c r="AE6" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF6" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG6" s="15"/>
       <c r="AH6" s="24" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="AI6" s="24" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="AJ6" s="23"/>
       <c r="AK6" s="23"/>
@@ -2491,15 +2505,15 @@
       <c r="BM6" s="23"/>
       <c r="BN6" s="23"/>
     </row>
-    <row r="7" spans="1:66">
+    <row r="7" spans="1:66" ht="15">
       <c r="A7" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>120</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>36</v>
@@ -2511,7 +2525,7 @@
         <v>104</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K7" s="21" t="s">
         <v>120</v>
@@ -2519,32 +2533,32 @@
       <c r="M7" s="26"/>
       <c r="N7" s="26"/>
       <c r="P7" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q7" s="21" t="s">
         <v>107</v>
       </c>
       <c r="S7" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T7" s="21" t="s">
         <v>107</v>
       </c>
       <c r="AE7" s="24" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AF7" s="24" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="AG7" s="15"/>
       <c r="AH7" s="24" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="AI7" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:66">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:66" ht="12.75">
       <c r="A8" s="19" t="s">
         <v>108</v>
       </c>
@@ -2552,7 +2566,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>36</v>
@@ -2564,32 +2578,26 @@
         <v>36</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q8" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S8" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="T8" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AE8" s="24" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AF8" s="24" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AG8" s="15"/>
-      <c r="AH8" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI8" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:66">
+    </row>
+    <row r="9" spans="1:66" ht="12.75">
       <c r="A9" s="19" t="s">
         <v>121</v>
       </c>
@@ -2597,10 +2605,10 @@
         <v>36</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>112</v>
@@ -2609,35 +2617,39 @@
         <v>36</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="Q9" s="21" t="s">
         <v>36</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="T9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
+      <c r="AE9" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF9" s="24" t="s">
+        <v>36</v>
+      </c>
       <c r="AG9" s="15"/>
       <c r="AH9" s="15"/>
       <c r="AI9" s="15"/>
     </row>
-    <row r="10" spans="1:66">
+    <row r="10" spans="1:66" ht="12.75">
       <c r="A10" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="AE10" s="15"/>
       <c r="AF10" s="15"/>
@@ -2645,9 +2657,9 @@
       <c r="AH10" s="15"/>
       <c r="AI10" s="15"/>
     </row>
-    <row r="11" spans="1:66">
+    <row r="11" spans="1:66" ht="12.75">
       <c r="A11" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>36</v>
@@ -2658,9 +2670,9 @@
       <c r="AH11" s="15"/>
       <c r="AI11" s="15"/>
     </row>
-    <row r="12" spans="1:66">
+    <row r="12" spans="1:66" ht="12.75">
       <c r="A12" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>36</v>
@@ -2671,12 +2683,12 @@
       <c r="AH12" s="15"/>
       <c r="AI12" s="15"/>
     </row>
-    <row r="13" spans="1:66">
+    <row r="13" spans="1:66" ht="12.75">
       <c r="A13" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AE13" s="15"/>
       <c r="AF13" s="15"/>
@@ -2684,12 +2696,12 @@
       <c r="AH13" s="15"/>
       <c r="AI13" s="15"/>
     </row>
-    <row r="14" spans="1:66">
+    <row r="14" spans="1:66" ht="12.75">
       <c r="A14" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="AE14" s="15"/>
       <c r="AF14" s="15"/>
@@ -2697,14 +2709,14 @@
       <c r="AH14" s="15"/>
       <c r="AI14" s="15"/>
     </row>
-    <row r="15" spans="1:66">
+    <row r="15" spans="1:66" ht="12.75">
       <c r="AE15" s="15"/>
       <c r="AF15" s="15"/>
       <c r="AG15" s="15"/>
       <c r="AH15" s="15"/>
       <c r="AI15" s="15"/>
     </row>
-    <row r="16" spans="1:66">
+    <row r="16" spans="1:66" ht="12.75">
       <c r="AE16" s="15"/>
       <c r="AF16" s="15"/>
       <c r="AG16" s="15"/>
@@ -2712,39 +2724,39 @@
       <c r="AI16" s="15"/>
     </row>
     <row r="17" spans="1:35" ht="15.75" customHeight="1">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="G17" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="32"/>
+      <c r="J17" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="K17" s="32"/>
+      <c r="P17" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q17" s="32"/>
+      <c r="V17" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37"/>
-      <c r="G17" s="34" t="s">
+      <c r="W17" s="32"/>
+      <c r="Y17" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="J17" s="34" t="s">
+      <c r="Z17" s="32"/>
+      <c r="AE17" s="36" t="s">
         <v>154</v>
-      </c>
-      <c r="K17" s="32"/>
-      <c r="P17" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q17" s="32"/>
-      <c r="V17" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="W17" s="32"/>
-      <c r="Y17" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z17" s="32"/>
-      <c r="AE17" s="35" t="s">
-        <v>158</v>
       </c>
       <c r="AF17" s="32"/>
       <c r="AG17" s="15"/>
-      <c r="AH17" s="35" t="s">
-        <v>159</v>
+      <c r="AH17" s="36" t="s">
+        <v>155</v>
       </c>
       <c r="AI17" s="32"/>
     </row>
@@ -2779,8 +2791,8 @@
       <c r="Q18" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="S18" s="34" t="s">
-        <v>160</v>
+      <c r="S18" s="31" t="s">
+        <v>156</v>
       </c>
       <c r="T18" s="32"/>
       <c r="V18" s="17" t="s">
@@ -2809,36 +2821,36 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" ht="15">
       <c r="A19" s="19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D19" s="28" t="s">
         <v>108</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G19" s="19" t="s">
         <v>108</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>106</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="P19" s="20" t="s">
         <v>106</v>
       </c>
       <c r="Q19" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S19" s="17" t="s">
         <v>103</v>
@@ -2850,52 +2862,52 @@
         <v>106</v>
       </c>
       <c r="W19" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Y19" s="20" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Z19" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AE19" s="22" t="s">
         <v>106</v>
       </c>
       <c r="AF19" s="22" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AG19" s="15"/>
-      <c r="AH19" s="22" t="s">
-        <v>106</v>
+      <c r="AH19" s="24" t="s">
+        <v>110</v>
       </c>
       <c r="AI19" s="22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" ht="12.75">
       <c r="A20" s="19" t="s">
         <v>108</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>112</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>112</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J20" s="21" t="s">
         <v>113</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="P20" s="21" t="s">
         <v>114</v>
@@ -2913,34 +2925,34 @@
         <v>115</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="Y20" s="21" t="s">
         <v>116</v>
       </c>
       <c r="Z20" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AE20" s="24" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="AF20" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AG20" s="15"/>
       <c r="AH20" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI20" s="22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" spans="1:35">
+        <v>127</v>
+      </c>
+      <c r="AI20" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" ht="12.75">
       <c r="A21" s="19" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
@@ -2966,54 +2978,54 @@
         <v>125</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Y21" s="21" t="s">
         <v>110</v>
       </c>
       <c r="Z21" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AE21" s="24" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="AF21" s="24" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="AG21" s="15"/>
       <c r="AH21" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI21" s="24" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35">
+        <v>177</v>
+      </c>
+      <c r="AI21" s="22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" ht="12.75">
       <c r="A22" s="19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D22" s="29"/>
       <c r="E22" s="29"/>
       <c r="J22" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="P22" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="K22" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="P22" s="21" t="s">
-        <v>133</v>
-      </c>
       <c r="Q22" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S22" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="T22" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="V22" s="30"/>
       <c r="W22" s="30"/>
@@ -3021,75 +3033,75 @@
         <v>117</v>
       </c>
       <c r="Z22" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AE22" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF22" s="24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AG22" s="15"/>
       <c r="AH22" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI22" s="22" t="s">
-        <v>162</v>
+        <v>179</v>
+      </c>
+      <c r="AI22" s="24" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:35" ht="15.75" customHeight="1">
       <c r="A23" s="19" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
-      <c r="G23" s="34" t="s">
-        <v>171</v>
+        <v>161</v>
+      </c>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
+      <c r="G23" s="31" t="s">
+        <v>167</v>
       </c>
       <c r="H23" s="32"/>
       <c r="J23" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="M23" s="30"/>
       <c r="N23" s="30"/>
       <c r="P23" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q23" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S23" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T23" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AE23" s="24" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="AF23" s="24" t="s">
         <v>163</v>
       </c>
       <c r="AG23" s="15"/>
       <c r="AH23" s="24" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="AI23" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" ht="15">
       <c r="A24" s="19" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D24" s="27" t="s">
         <v>103</v>
@@ -3104,124 +3116,118 @@
         <v>104</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q24" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S24" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="T24" s="20" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AE24" s="24" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AF24" s="24" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="AG24" s="15"/>
-      <c r="AH24" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI24" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:35">
+    </row>
+    <row r="25" spans="1:35" ht="12.75">
       <c r="A25" s="19" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>109</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G25" s="19" t="s">
         <v>109</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="Q25" s="21" t="s">
         <v>36</v>
       </c>
       <c r="S25" s="21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="T25" s="21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="1:35">
+      <c r="AE25" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF25" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" ht="12.75">
       <c r="A26" s="19" t="s">
         <v>121</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" ht="12.75">
       <c r="A27" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" ht="12.75">
       <c r="A28" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" ht="12.75">
       <c r="A29" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" ht="12.75">
+      <c r="A30" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" spans="1:35">
-      <c r="A30" s="19" t="s">
-        <v>147</v>
-      </c>
       <c r="B30" s="19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" ht="12.75">
       <c r="A31" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="V17:W17"/>
     <mergeCell ref="Y17:Z17"/>
     <mergeCell ref="AE17:AF17"/>
@@ -3230,12 +3236,18 @@
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="V1:W1"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="P17:Q17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
